--- a/data/trans_bre/P6905-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 30,43</t>
+          <t>-4,67; 31,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 43,2</t>
+          <t>1,31; 43,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 40,35</t>
+          <t>-0,84; 44,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 27,75</t>
+          <t>-5,29; 27,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 324,21</t>
+          <t>-35,29; 356,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 217,98</t>
+          <t>1,54; 222,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 234,96</t>
+          <t>-7,28; 270,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 365,68</t>
+          <t>-25,28; 324,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 25,91</t>
+          <t>-5,12; 25,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 40,83</t>
+          <t>8,53; 38,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 26,61</t>
+          <t>-5,11; 25,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 23,9</t>
+          <t>-1,71; 24,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 106,44</t>
+          <t>-15,52; 104,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,69; 241,37</t>
+          <t>28,79; 221,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 179,48</t>
+          <t>-20,85; 159,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 146,99</t>
+          <t>-7,16; 152,3</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 33,13</t>
+          <t>-1,6; 34,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 18,27</t>
+          <t>-14,89; 17,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 26,19</t>
+          <t>-1,59; 27,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 29,34</t>
+          <t>-18,99; 27,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 135,69</t>
+          <t>-2,59; 135,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 83,06</t>
+          <t>-38,8; 74,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 105,14</t>
+          <t>-5,85; 108,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 212,2</t>
+          <t>-59,16; 199,76</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 18,13</t>
+          <t>-7,26; 18,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 28,92</t>
+          <t>-3,52; 29,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 31,96</t>
+          <t>-3,65; 30,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 19,02</t>
+          <t>-8,51; 20,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 56,03</t>
+          <t>-16,78; 57,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 175,52</t>
+          <t>-11,39; 172,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 134,47</t>
+          <t>-9,32; 122,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 84,75</t>
+          <t>-23,91; 85,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,85</t>
+          <t>3,01; 18,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 23,46</t>
+          <t>5,79; 22,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 22,74</t>
+          <t>5,18; 22,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 17,46</t>
+          <t>-0,18; 17,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 70,17</t>
+          <t>8,28; 67,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 104,06</t>
+          <t>19,1; 100,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 96,42</t>
+          <t>17,0; 94,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 91,13</t>
+          <t>-0,15; 89,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6905-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,94</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 31,32</t>
+          <t>-4,68; 32,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 43,83</t>
+          <t>2,23; 44,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 44,09</t>
+          <t>0,61; 44,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 27,21</t>
+          <t>-5,62; 26,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 356,54</t>
+          <t>-30,04; 345,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 222,91</t>
+          <t>1,38; 228,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 270,16</t>
+          <t>3,18; 311,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 324,52</t>
+          <t>-26,83; 316,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 25,94</t>
+          <t>-6,32; 25,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 38,96</t>
+          <t>8,44; 40,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 25,45</t>
+          <t>-4,9; 27,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 24,06</t>
+          <t>-7,13; 17,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 104,14</t>
+          <t>-19,72; 100,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 221,22</t>
+          <t>26,14; 218,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 159,84</t>
+          <t>-18,79; 204,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 152,3</t>
+          <t>-20,58; 91,42</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>18,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 34,11</t>
+          <t>-0,85; 32,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 17,36</t>
+          <t>-14,55; 18,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 27,06</t>
+          <t>-2,43; 27,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 27,58</t>
+          <t>2,51; 32,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 135,67</t>
+          <t>-4,97; 130,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 74,35</t>
+          <t>-40,93; 78,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 108,44</t>
+          <t>-6,89; 110,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,16; 199,76</t>
+          <t>6,12; 235,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 18,73</t>
+          <t>-9,58; 16,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 29,42</t>
+          <t>-3,39; 26,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 30,34</t>
+          <t>-0,57; 31,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 20,12</t>
+          <t>-11,28; 14,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 57,63</t>
+          <t>-21,48; 50,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 172,99</t>
+          <t>-13,46; 147,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 122,45</t>
+          <t>-2,72; 130,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 85,94</t>
+          <t>-29,52; 62,0</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,75</t>
+          <t>2,9; 19,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,76</t>
+          <t>6,83; 24,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 22,52</t>
+          <t>5,42; 22,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 17,74</t>
+          <t>1,56; 15,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 67,27</t>
+          <t>8,99; 71,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 100,31</t>
+          <t>22,47; 105,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 94,61</t>
+          <t>16,84; 95,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 89,57</t>
+          <t>4,93; 71,85</t>
         </is>
       </c>
     </row>
